--- a/output/pdf_financials_xlsx/KIP.xlsx
+++ b/output/pdf_financials_xlsx/KIP.xlsx
@@ -4475,13 +4475,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.23285</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.283481</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.328523</v>
       </c>
       <c r="E92" s="1" t="inlineStr">
         <is>
@@ -4494,10 +4494,10 @@
         </is>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.328523</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.328523</v>
       </c>
       <c r="I92" s="1" t="inlineStr">
         <is>
@@ -7392,7 +7392,11 @@
           <t>Share-based payments reserve (note 8)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -8174,7 +8178,11 @@
           <t>Share-based payments reserve (note 9)</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -8776,7 +8784,11 @@
           <t>Share-based payments reserve (note 10)</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" s="5" t="n">
         <v>1.23285</v>
       </c>

--- a/output/pdf_financials_xlsx/KIP.xlsx
+++ b/output/pdf_financials_xlsx/KIP.xlsx
@@ -831,16 +831,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.010918</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.003713</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.002703</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.00042</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -852,13 +852,13 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.020649</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.044433</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.028238</v>
       </c>
     </row>
     <row r="13">
@@ -1452,13 +1452,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.359952</v>
+        <v>-0.37087</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.999369</v>
+        <v>-1.003082</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.389023</v>
+        <v>-2.391726</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -1477,13 +1477,13 @@
         <v>-0.436822</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.748968</v>
+        <v>-0.769617</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.194274</v>
+        <v>-0.238707</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.203167</v>
+        <v>-0.231405</v>
       </c>
     </row>
     <row r="28">
@@ -1530,13 +1530,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.359952</v>
+        <v>-0.37087</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.999369</v>
+        <v>-1.003082</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.389023</v>
+        <v>-2.391726</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -1555,13 +1555,13 @@
         <v>-0.436822</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.748968</v>
+        <v>-0.769617</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.194274</v>
+        <v>-0.238707</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.203167</v>
+        <v>-0.231405</v>
       </c>
     </row>
     <row r="30">
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.367824</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.771402</v>
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.034053</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.044546</v>
       </c>
       <c r="I34" s="1" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.7</v>
+        <v>1.067824</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.771402</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.034053</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.044546</v>
       </c>
       <c r="I36" s="1" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.383671</v>
+        <v>0.015847</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.380417</v>
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.336241</v>
+        <v>0.302188</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.044546</v>
+        <v>0</v>
       </c>
       <c r="I48" s="1" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -12232,7 +12232,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -19968,7 +19968,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E229" s="5" t="n">
